--- a/output/status_live.xlsx
+++ b/output/status_live.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="358">
   <si>
     <t>PNR</t>
   </si>
@@ -40,238 +40,1051 @@
     <t>Error</t>
   </si>
   <si>
-    <t>A1ETUC</t>
-  </si>
-  <si>
-    <t>SAWHNEY</t>
-  </si>
-  <si>
-    <t>CONFIRMED</t>
-  </si>
-  <si>
-    <t>BOARDED</t>
+    <t>A22U4P</t>
+  </si>
+  <si>
+    <t>SACHINBAHL30@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CONFIRMED (2)</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2) | P2:BOARDED (2) | P3:BOARDED (2) | P4:BOARDED (2) | P5:BOARDED (2)</t>
   </si>
   <si>
     <t>NO</t>
   </si>
   <si>
+    <t>IX 127</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:26:47.767Z</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>2026-03-31T19:30:44.844Z</t>
-  </si>
-  <si>
-    <t>AZN2TC</t>
-  </si>
-  <si>
-    <t>SINGH</t>
-  </si>
-  <si>
-    <t>6E2192</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:31:00.511Z</t>
-  </si>
-  <si>
-    <t>BV14SV</t>
-  </si>
-  <si>
-    <t>RANPISE</t>
-  </si>
-  <si>
-    <t>6E6197</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:31:15.391Z</t>
-  </si>
-  <si>
-    <t>BZRBVS</t>
-  </si>
-  <si>
-    <t>6E252</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:31:29.420Z</t>
-  </si>
-  <si>
-    <t>L7JIYG</t>
-  </si>
-  <si>
-    <t>SAHARAWAT</t>
-  </si>
-  <si>
-    <t>COMPLETED</t>
-  </si>
-  <si>
-    <t>NOSHOW</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>6E698</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:31:44.657Z</t>
-  </si>
-  <si>
-    <t>Y2IENV</t>
-  </si>
-  <si>
-    <t>ARORA</t>
-  </si>
-  <si>
-    <t>6E5015</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:31:59.509Z</t>
-  </si>
-  <si>
-    <t>C73TRT</t>
-  </si>
-  <si>
-    <t>CHADHA</t>
-  </si>
-  <si>
-    <t>6E5315</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:32:14.877Z</t>
-  </si>
-  <si>
-    <t>U34JXV</t>
-  </si>
-  <si>
-    <t>SONI</t>
-  </si>
-  <si>
-    <t>6E2111</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:32:28.437Z</t>
-  </si>
-  <si>
-    <t>U8L59Q</t>
-  </si>
-  <si>
-    <t>6E1106</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:32:44.364Z</t>
-  </si>
-  <si>
-    <t>B93KVH</t>
-  </si>
-  <si>
-    <t>CANCELLED</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:33:00.642Z</t>
-  </si>
-  <si>
-    <t>D6Y32N</t>
-  </si>
-  <si>
-    <t>KUMAR</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:33:13.317Z</t>
-  </si>
-  <si>
-    <t>HZRG9C</t>
-  </si>
-  <si>
-    <t>SRIVASTAVA</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:33:28.789Z</t>
-  </si>
-  <si>
-    <t>I7JKNN</t>
-  </si>
-  <si>
-    <t>SHARMA</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:33:43.673Z</t>
-  </si>
-  <si>
-    <t>O4L4KW</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:33:58.898Z</t>
-  </si>
-  <si>
-    <t>J3V3SZ</t>
-  </si>
-  <si>
-    <t>KATHIRIYA</t>
-  </si>
-  <si>
-    <t>HOLDCANCELLED</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:34:14.565Z</t>
-  </si>
-  <si>
-    <t>K9NNYH</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:34:27.925Z</t>
-  </si>
-  <si>
-    <t>MZW7FS</t>
-  </si>
-  <si>
-    <t>PHARANDE</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:34:42.973Z</t>
-  </si>
-  <si>
-    <t>N9232H</t>
-  </si>
-  <si>
-    <t>JAIN</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:34:59.874Z</t>
-  </si>
-  <si>
-    <t>PZRCTV</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:35:14.536Z</t>
-  </si>
-  <si>
-    <t>QVH6KI</t>
-  </si>
-  <si>
-    <t>RIBADIYA</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:35:29.324Z</t>
-  </si>
-  <si>
-    <t>R2HDPP</t>
-  </si>
-  <si>
-    <t>BEGUM</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:35:42.983Z</t>
-  </si>
-  <si>
-    <t>S3DC4Z</t>
-  </si>
-  <si>
-    <t>RAM</t>
-  </si>
-  <si>
-    <t>2026-03-31T19:35:56.510Z</t>
+    <t>A4YGTM</t>
+  </si>
+  <si>
+    <t>AZAADTRAVELS58@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2)</t>
+  </si>
+  <si>
+    <t>IX 183</t>
+  </si>
+  <si>
+    <t>2025-04-05</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:26:56.067Z</t>
+  </si>
+  <si>
+    <t>A5CLXJ</t>
+  </si>
+  <si>
+    <t>TICKETING@SHIV-TRAVEL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:27:22.083Z</t>
+  </si>
+  <si>
+    <t>page.waitForResponse: Timeout 20000ms exceeded while waiting for event "response"</t>
+  </si>
+  <si>
+    <t>B6UHYT</t>
+  </si>
+  <si>
+    <t>IX 191</t>
+  </si>
+  <si>
+    <t>2025-04-11</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:27:29.098Z</t>
+  </si>
+  <si>
+    <t>BV3C6Y</t>
+  </si>
+  <si>
+    <t>INFO@TRAVELVILLAGE.DEALS</t>
+  </si>
+  <si>
+    <t>CANCELLED (3)</t>
+  </si>
+  <si>
+    <t>IX 192</t>
+  </si>
+  <si>
+    <t>2025-04-19</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:27:36.963Z</t>
+  </si>
+  <si>
+    <t>C7954A</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2) | P2:BOARDED (2) | P3:BOARDED (2)</t>
+  </si>
+  <si>
+    <t>2025-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:27:45.150Z</t>
+  </si>
+  <si>
+    <t>CBIS4R</t>
+  </si>
+  <si>
+    <t>FYI.PVT.LTD@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2513</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:27:52.001Z</t>
+  </si>
+  <si>
+    <t>CYBIPX</t>
+  </si>
+  <si>
+    <t>RAJIVINDU1996@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1956</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:00.568Z</t>
+  </si>
+  <si>
+    <t>D3QS3Z</t>
+  </si>
+  <si>
+    <t>TRAVELTRUSTJPR@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1198</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:10.220Z</t>
+  </si>
+  <si>
+    <t>D7QFFQ</t>
+  </si>
+  <si>
+    <t>IX 491</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:18.219Z</t>
+  </si>
+  <si>
+    <t>DBJNKE</t>
+  </si>
+  <si>
+    <t>IX 193</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:25.084Z</t>
+  </si>
+  <si>
+    <t>DBS2QE</t>
+  </si>
+  <si>
+    <t>NVENUSAS@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>2025-04-17</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:34.392Z</t>
+  </si>
+  <si>
+    <t>DUQE7Y</t>
+  </si>
+  <si>
+    <t>TICKETING@IFLYVACATIONS.COM</t>
+  </si>
+  <si>
+    <t>P1:NO_SHOW (3)</t>
+  </si>
+  <si>
+    <t>IX 2650</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:41.748Z</t>
+  </si>
+  <si>
+    <t>DZT5TV</t>
+  </si>
+  <si>
+    <t>BHAKTITRAVELSANDSERVICES@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1144</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:50.573Z</t>
+  </si>
+  <si>
+    <t>E2CB2P</t>
+  </si>
+  <si>
+    <t>V2HOLIDAYS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2) | P2:BOARDED (2) | P3:BOARDED (2) | P4:BOARDED (2)</t>
+  </si>
+  <si>
+    <t>IX 241</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:28:57.756Z</t>
+  </si>
+  <si>
+    <t>E5KIHW</t>
+  </si>
+  <si>
+    <t>BOOKINGS@TRAVELOWORLD.IN</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2) | P2:BOARDED (2)</t>
+  </si>
+  <si>
+    <t>IX 2696</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:04.914Z</t>
+  </si>
+  <si>
+    <t>E8R3XA</t>
+  </si>
+  <si>
+    <t>OMPSTOURS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2714</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:14.583Z</t>
+  </si>
+  <si>
+    <t>F6GHNT</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:22.403Z</t>
+  </si>
+  <si>
+    <t>F6VZTT</t>
+  </si>
+  <si>
+    <t>TARUN@SRIYAAN.CO.IN</t>
+  </si>
+  <si>
+    <t>IX 1176</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:30.240Z</t>
+  </si>
+  <si>
+    <t>F81EFA</t>
+  </si>
+  <si>
+    <t>DESTINY7TRAVELS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2011</t>
+  </si>
+  <si>
+    <t>2025-04-12</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:39.313Z</t>
+  </si>
+  <si>
+    <t>FB1PHH</t>
+  </si>
+  <si>
+    <t>DECCAN.TOUR@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:46.466Z</t>
+  </si>
+  <si>
+    <t>FCYZVE</t>
+  </si>
+  <si>
+    <t>NUMINOUSHOLIDAY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>P1:NA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:29:53.494Z</t>
+  </si>
+  <si>
+    <t>FZY9SY</t>
+  </si>
+  <si>
+    <t>IX 113</t>
+  </si>
+  <si>
+    <t>2025-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:00.316Z</t>
+  </si>
+  <si>
+    <t>G1K4JF</t>
+  </si>
+  <si>
+    <t>IX 2547</t>
+  </si>
+  <si>
+    <t>2025-04-22</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:09.090Z</t>
+  </si>
+  <si>
+    <t>G1Z3FI</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:19.062Z</t>
+  </si>
+  <si>
+    <t>G3SK7M</t>
+  </si>
+  <si>
+    <t>IX 145</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:27.509Z</t>
+  </si>
+  <si>
+    <t>G87K3N</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:34.474Z</t>
+  </si>
+  <si>
+    <t>GC61QE</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:43.404Z</t>
+  </si>
+  <si>
+    <t>H1HJXV</t>
+  </si>
+  <si>
+    <t>TTRAVELICIOUS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1331</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:49.892Z</t>
+  </si>
+  <si>
+    <t>H6VHTT</t>
+  </si>
+  <si>
+    <t>GIRIMANAT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 168</t>
+  </si>
+  <si>
+    <t>2025-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:30:59.873Z</t>
+  </si>
+  <si>
+    <t>H73L6Q</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:08.402Z</t>
+  </si>
+  <si>
+    <t>H8BUYQ</t>
+  </si>
+  <si>
+    <t>MUFADDALTRAVEL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:17.559Z</t>
+  </si>
+  <si>
+    <t>H9RPGK</t>
+  </si>
+  <si>
+    <t>BHAVNA.SUSWAL@TSCPL.BIZ</t>
+  </si>
+  <si>
+    <t>IX 137</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:26.170Z</t>
+  </si>
+  <si>
+    <t>HBCU4E</t>
+  </si>
+  <si>
+    <t>PLANYOURTRAVEL2019@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1068</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:33.023Z</t>
+  </si>
+  <si>
+    <t>HC8FKR</t>
+  </si>
+  <si>
+    <t>GAURAV@TRAVELONWHEELS.IN</t>
+  </si>
+  <si>
+    <t>IX 1937</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:41.071Z</t>
+  </si>
+  <si>
+    <t>I25HQF</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:49.745Z</t>
+  </si>
+  <si>
+    <t>I8F2FA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:31:57.932Z</t>
+  </si>
+  <si>
+    <t>IUBQSB</t>
+  </si>
+  <si>
+    <t>IX 2665</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:32:06.087Z</t>
+  </si>
+  <si>
+    <t>IVCU6Y</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:32:14.139Z</t>
+  </si>
+  <si>
+    <t>J1R39S</t>
+  </si>
+  <si>
+    <t>RISHABH7709@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:32:23.767Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:35:33.734Z</t>
+  </si>
+  <si>
+    <t>J3JT2M</t>
+  </si>
+  <si>
+    <t>BOOKNFLY112@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2511</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:35:41.509Z</t>
+  </si>
+  <si>
+    <t>J4ND8J</t>
+  </si>
+  <si>
+    <t>IX 2542</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:35:51.128Z</t>
+  </si>
+  <si>
+    <t>J5VC8G</t>
+  </si>
+  <si>
+    <t>IX 1676</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:35:58.164Z</t>
+  </si>
+  <si>
+    <t>JBBIQH</t>
+  </si>
+  <si>
+    <t>GTRAVELSBNL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1200</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:04.977Z</t>
+  </si>
+  <si>
+    <t>JBE1NH</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:13.049Z</t>
+  </si>
+  <si>
+    <t>K3LE6M</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:22.467Z</t>
+  </si>
+  <si>
+    <t>K5JVNJ</t>
+  </si>
+  <si>
+    <t>TRAVELSGEHLOT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 196</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:31.759Z</t>
+  </si>
+  <si>
+    <t>KBWL7E</t>
+  </si>
+  <si>
+    <t>IX 2752</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:40.392Z</t>
+  </si>
+  <si>
+    <t>L1DHJV</t>
+  </si>
+  <si>
+    <t>IX 1199</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:47.967Z</t>
+  </si>
+  <si>
+    <t>L638UJ</t>
+  </si>
+  <si>
+    <t>IX 2791</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:36:55.964Z</t>
+  </si>
+  <si>
+    <t>L6JLWW</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:05.780Z</t>
+  </si>
+  <si>
+    <t>LCNMNR</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:14.165Z</t>
+  </si>
+  <si>
+    <t>LDYYGB</t>
+  </si>
+  <si>
+    <t>2025-04-15</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:22.650Z</t>
+  </si>
+  <si>
+    <t>LZHNYL</t>
+  </si>
+  <si>
+    <t>TRAVEL@YOLOO.IN</t>
+  </si>
+  <si>
+    <t>P1:BOARDED (2) | P2:BOARDED (2) | P3:BOARDED (2) | P4:BOARDED (2) | P5:BOARDED (2) | P6:BOARDED (2)</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:31.264Z</t>
+  </si>
+  <si>
+    <t>M2VJYS</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:40.577Z</t>
+  </si>
+  <si>
+    <t>M8LR5N</t>
+  </si>
+  <si>
+    <t>S2SHOLIDAYS1997@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2872</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:48.995Z</t>
+  </si>
+  <si>
+    <t>M9R6SN</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:37:58.736Z</t>
+  </si>
+  <si>
+    <t>MB923U</t>
+  </si>
+  <si>
+    <t>ADHYAHOLIDAYS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>P1:NA | P2:NA | P3:NA | P4:NA | P5:NA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:06.615Z</t>
+  </si>
+  <si>
+    <t>MZ5F4Y</t>
+  </si>
+  <si>
+    <t>KIRANTRAVEL2017@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 1153</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:15.230Z</t>
+  </si>
+  <si>
+    <t>MZV97V</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:24.135Z</t>
+  </si>
+  <si>
+    <t>N1HIKV</t>
+  </si>
+  <si>
+    <t>INFO@TRAVONIKA.COM</t>
+  </si>
+  <si>
+    <t>P1:NA | P2:NA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:30.772Z</t>
+  </si>
+  <si>
+    <t>O3YDFC</t>
+  </si>
+  <si>
+    <t>2025-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:38.362Z</t>
+  </si>
+  <si>
+    <t>OCZQ2R</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:47.310Z</t>
+  </si>
+  <si>
+    <t>P5PDHJ</t>
+  </si>
+  <si>
+    <t>IX 2760</t>
+  </si>
+  <si>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:38:57.193Z</t>
+  </si>
+  <si>
+    <t>P5U9RJ</t>
+  </si>
+  <si>
+    <t>IX 1012</t>
+  </si>
+  <si>
+    <t>2025-04-20</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:04.294Z</t>
+  </si>
+  <si>
+    <t>PD2KQR</t>
+  </si>
+  <si>
+    <t>IX 255</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:11.625Z</t>
+  </si>
+  <si>
+    <t>Q49W9M</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:20.000Z</t>
+  </si>
+  <si>
+    <t>Q911NA</t>
+  </si>
+  <si>
+    <t>IX 494</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:27.384Z</t>
+  </si>
+  <si>
+    <t>S1ZPKY</t>
+  </si>
+  <si>
+    <t>SAGARSTARATE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:34.578Z</t>
+  </si>
+  <si>
+    <t>S27MHV</t>
+  </si>
+  <si>
+    <t>IX 2546</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:43.104Z</t>
+  </si>
+  <si>
+    <t>S28UQV</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:50.414Z</t>
+  </si>
+  <si>
+    <t>S2KZXV</t>
+  </si>
+  <si>
+    <t>HARDEV20000IN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2025-06-11</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:39:57.473Z</t>
+  </si>
+  <si>
+    <t>S2RKMF</t>
+  </si>
+  <si>
+    <t>IX 1169</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:06.018Z</t>
+  </si>
+  <si>
+    <t>S3G2TF</t>
+  </si>
+  <si>
+    <t>2025-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:15.834Z</t>
+  </si>
+  <si>
+    <t>S8C8RD</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:23.123Z</t>
+  </si>
+  <si>
+    <t>S8DNTD</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:31.109Z</t>
+  </si>
+  <si>
+    <t>T1KVSY</t>
+  </si>
+  <si>
+    <t>SUDANSHU786.CA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 164</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:38.711Z</t>
+  </si>
+  <si>
+    <t>T3VTPC</t>
+  </si>
+  <si>
+    <t>IX 195</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:49.015Z</t>
+  </si>
+  <si>
+    <t>TB6W6H</t>
+  </si>
+  <si>
+    <t>NARAYANLALJI1584@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2025-04-23</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:40:55.822Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:06.485Z</t>
+  </si>
+  <si>
+    <t>UD247R</t>
+  </si>
+  <si>
+    <t>IX 173</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:15.018Z</t>
+  </si>
+  <si>
+    <t>V7SEWG</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:24.139Z</t>
+  </si>
+  <si>
+    <t>V9LJRA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:33.037Z</t>
+  </si>
+  <si>
+    <t>VBQW4U</t>
+  </si>
+  <si>
+    <t>TEJAS.VAISHNAV@MILESTONEHOLIDAYS.CO.IN</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:42.302Z</t>
+  </si>
+  <si>
+    <t>VYTCQK</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:49.453Z</t>
+  </si>
+  <si>
+    <t>VZJG5Y</t>
+  </si>
+  <si>
+    <t>IX 1954</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:44:58.697Z</t>
+  </si>
+  <si>
+    <t>W8R7JQ</t>
+  </si>
+  <si>
+    <t>IX 1227</t>
+  </si>
+  <si>
+    <t>2025-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:08.395Z</t>
+  </si>
+  <si>
+    <t>X48KYC</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:17.194Z</t>
+  </si>
+  <si>
+    <t>X4IPKP</t>
+  </si>
+  <si>
+    <t>WTTRAVELDEL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:25.418Z</t>
+  </si>
+  <si>
+    <t>X4P2WP</t>
+  </si>
+  <si>
+    <t>ARPITDESAIDHG@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>P1:NA | P2:NA | P3:NA | P4:NA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:33.593Z</t>
+  </si>
+  <si>
+    <t>X7YJYW</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:42.395Z</t>
+  </si>
+  <si>
+    <t>X8JZND</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:49.540Z</t>
+  </si>
+  <si>
+    <t>X8RD4A</t>
+  </si>
+  <si>
+    <t>IX 832</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:45:56.352Z</t>
+  </si>
+  <si>
+    <t>XZ5H4L</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:05.258Z</t>
+  </si>
+  <si>
+    <t>Y7U4YG</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:14.039Z</t>
+  </si>
+  <si>
+    <t>Y9F1NQ</t>
+  </si>
+  <si>
+    <t>TRAVELPOINTJPR@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IX 2768</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:22.365Z</t>
+  </si>
+  <si>
+    <t>Y9ILNA</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:31.015Z</t>
+  </si>
+  <si>
+    <t>Y9VETA</t>
+  </si>
+  <si>
+    <t>IX 1142</t>
+  </si>
+  <si>
+    <t>2025-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:42.574Z</t>
+  </si>
+  <si>
+    <t>YC4THH</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:46:52.520Z</t>
+  </si>
+  <si>
+    <t>ZDZD5R</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:47:01.428Z</t>
+  </si>
+  <si>
+    <t>ZUTPSR</t>
+  </si>
+  <si>
+    <t>GURPREETLOE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:47:10.360Z</t>
   </si>
 </sst>
 </file>
@@ -658,7 +1471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -719,622 +1532,2942 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
         <v>40</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="H22" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" t="s">
+        <v>143</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>145</v>
+      </c>
+      <c r="H32" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" t="s">
+        <v>153</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" t="s">
+        <v>109</v>
+      </c>
+      <c r="H37" t="s">
+        <v>164</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" t="s">
         <v>85</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" t="s">
+        <v>172</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>152</v>
+      </c>
+      <c r="G41" t="s">
+        <v>61</v>
+      </c>
+      <c r="H41" t="s">
+        <v>175</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" t="s">
+        <v>176</v>
+      </c>
+      <c r="I42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" t="s">
         <v>65</v>
       </c>
-      <c r="D23" t="s">
+      <c r="H43" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G44" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" t="s">
+        <v>186</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" t="s">
+        <v>189</v>
+      </c>
+      <c r="G46" t="s">
+        <v>190</v>
+      </c>
+      <c r="H46" t="s">
+        <v>191</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
+        <v>193</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" t="s">
+        <v>190</v>
+      </c>
+      <c r="H48" t="s">
+        <v>195</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>198</v>
+      </c>
+      <c r="G49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" t="s">
+        <v>199</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>200</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H50" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>204</v>
+      </c>
+      <c r="G51" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" t="s">
+        <v>205</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>207</v>
+      </c>
+      <c r="G52" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" t="s">
+        <v>209</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H53" t="s">
+        <v>211</v>
+      </c>
+      <c r="I53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54" t="s">
+        <v>214</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>29</v>
+      </c>
+      <c r="G55" t="s">
+        <v>216</v>
+      </c>
+      <c r="H55" t="s">
+        <v>217</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s">
+        <v>221</v>
+      </c>
+      <c r="H56" t="s">
+        <v>222</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>223</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>201</v>
+      </c>
+      <c r="G57" t="s">
+        <v>190</v>
+      </c>
+      <c r="H57" t="s">
+        <v>224</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" t="s">
+        <v>227</v>
+      </c>
+      <c r="G58" t="s">
+        <v>142</v>
+      </c>
+      <c r="H58" t="s">
+        <v>228</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" t="s">
+        <v>230</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" t="s">
+        <v>233</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" t="s">
+        <v>234</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" t="s">
+        <v>236</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>237</v>
+      </c>
+      <c r="G61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H61" t="s">
+        <v>238</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>239</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
         <v>14</v>
       </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>240</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" t="s">
+        <v>244</v>
+      </c>
+      <c r="I63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
+        <v>198</v>
+      </c>
+      <c r="G64" t="s">
+        <v>246</v>
+      </c>
+      <c r="H64" t="s">
+        <v>247</v>
+      </c>
+      <c r="I64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>201</v>
+      </c>
+      <c r="G65" t="s">
+        <v>190</v>
+      </c>
+      <c r="H65" t="s">
+        <v>249</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>251</v>
+      </c>
+      <c r="G66" t="s">
+        <v>252</v>
+      </c>
+      <c r="H66" t="s">
+        <v>253</v>
+      </c>
+      <c r="I66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
         <v>86</v>
       </c>
-      <c r="I23" t="s">
-        <v>14</v>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>255</v>
+      </c>
+      <c r="G67" t="s">
+        <v>256</v>
+      </c>
+      <c r="H67" t="s">
+        <v>257</v>
+      </c>
+      <c r="I67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>258</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>259</v>
+      </c>
+      <c r="G68" t="s">
+        <v>105</v>
+      </c>
+      <c r="H68" t="s">
+        <v>260</v>
+      </c>
+      <c r="I68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>261</v>
+      </c>
+      <c r="B69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>152</v>
+      </c>
+      <c r="G69" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" t="s">
+        <v>262</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>264</v>
+      </c>
+      <c r="G70" t="s">
+        <v>252</v>
+      </c>
+      <c r="H70" t="s">
+        <v>265</v>
+      </c>
+      <c r="I70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" t="s">
+        <v>267</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>168</v>
+      </c>
+      <c r="G71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" t="s">
+        <v>268</v>
+      </c>
+      <c r="I71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>270</v>
+      </c>
+      <c r="G72" t="s">
+        <v>36</v>
+      </c>
+      <c r="H72" t="s">
+        <v>271</v>
+      </c>
+      <c r="I72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>126</v>
+      </c>
+      <c r="G73" t="s">
+        <v>273</v>
+      </c>
+      <c r="H73" t="s">
+        <v>274</v>
+      </c>
+      <c r="I73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" t="s">
+        <v>276</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>91</v>
+      </c>
+      <c r="G74" t="s">
+        <v>277</v>
+      </c>
+      <c r="H74" t="s">
+        <v>278</v>
+      </c>
+      <c r="I74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>279</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>280</v>
+      </c>
+      <c r="G75" t="s">
+        <v>61</v>
+      </c>
+      <c r="H75" t="s">
+        <v>281</v>
+      </c>
+      <c r="I75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>282</v>
+      </c>
+      <c r="B76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>152</v>
+      </c>
+      <c r="G76" t="s">
+        <v>283</v>
+      </c>
+      <c r="H76" t="s">
+        <v>284</v>
+      </c>
+      <c r="I76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" t="s">
+        <v>286</v>
+      </c>
+      <c r="I77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>287</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" t="s">
+        <v>288</v>
+      </c>
+      <c r="I78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>289</v>
+      </c>
+      <c r="B79" t="s">
+        <v>290</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>291</v>
+      </c>
+      <c r="G79" t="s">
+        <v>161</v>
+      </c>
+      <c r="H79" t="s">
+        <v>292</v>
+      </c>
+      <c r="I79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>294</v>
+      </c>
+      <c r="G80" t="s">
+        <v>295</v>
+      </c>
+      <c r="H80" t="s">
+        <v>296</v>
+      </c>
+      <c r="I80" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>297</v>
+      </c>
+      <c r="B81" t="s">
+        <v>298</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>91</v>
+      </c>
+      <c r="G81" t="s">
+        <v>299</v>
+      </c>
+      <c r="H81" t="s">
+        <v>300</v>
+      </c>
+      <c r="I81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" t="s">
+        <v>301</v>
+      </c>
+      <c r="I82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>302</v>
+      </c>
+      <c r="B83" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>303</v>
+      </c>
+      <c r="G83" t="s">
+        <v>295</v>
+      </c>
+      <c r="H83" t="s">
+        <v>304</v>
+      </c>
+      <c r="I83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>305</v>
+      </c>
+      <c r="B84" t="s">
+        <v>108</v>
+      </c>
+      <c r="C84" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" t="s">
+        <v>243</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" t="s">
+        <v>306</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>307</v>
+      </c>
+      <c r="B85" t="s">
+        <v>267</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="s">
+        <v>86</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>255</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>308</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>309</v>
+      </c>
+      <c r="B86" t="s">
+        <v>310</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
+        <v>86</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>81</v>
+      </c>
+      <c r="G86" t="s">
+        <v>49</v>
+      </c>
+      <c r="H86" t="s">
+        <v>311</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>312</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" t="s">
+        <v>30</v>
+      </c>
+      <c r="H87" t="s">
+        <v>313</v>
+      </c>
+      <c r="I87" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>314</v>
+      </c>
+      <c r="B88" t="s">
+        <v>47</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>315</v>
+      </c>
+      <c r="G88" t="s">
+        <v>161</v>
+      </c>
+      <c r="H88" t="s">
+        <v>316</v>
+      </c>
+      <c r="I88" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>317</v>
+      </c>
+      <c r="B89" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>318</v>
+      </c>
+      <c r="G89" t="s">
+        <v>319</v>
+      </c>
+      <c r="H89" t="s">
+        <v>320</v>
+      </c>
+      <c r="I89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>321</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>303</v>
+      </c>
+      <c r="G90" t="s">
+        <v>208</v>
+      </c>
+      <c r="H90" t="s">
+        <v>322</v>
+      </c>
+      <c r="I90" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>323</v>
+      </c>
+      <c r="B91" t="s">
+        <v>324</v>
+      </c>
+      <c r="C91" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" t="s">
+        <v>243</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" t="s">
+        <v>325</v>
+      </c>
+      <c r="I91" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>326</v>
+      </c>
+      <c r="B92" t="s">
+        <v>327</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>328</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" t="s">
+        <v>329</v>
+      </c>
+      <c r="I92" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>330</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
+        <v>126</v>
+      </c>
+      <c r="G93" t="s">
+        <v>65</v>
+      </c>
+      <c r="H93" t="s">
+        <v>331</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>332</v>
+      </c>
+      <c r="B94" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" t="s">
+        <v>333</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>334</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
+        <v>335</v>
+      </c>
+      <c r="G95" t="s">
+        <v>36</v>
+      </c>
+      <c r="H95" t="s">
+        <v>336</v>
+      </c>
+      <c r="I95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>337</v>
+      </c>
+      <c r="B96" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>141</v>
+      </c>
+      <c r="G96" t="s">
+        <v>142</v>
+      </c>
+      <c r="H96" t="s">
+        <v>338</v>
+      </c>
+      <c r="I96" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>339</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" t="s">
+        <v>29</v>
+      </c>
+      <c r="G97" t="s">
+        <v>216</v>
+      </c>
+      <c r="H97" t="s">
+        <v>340</v>
+      </c>
+      <c r="I97" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>341</v>
+      </c>
+      <c r="B98" t="s">
+        <v>342</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" t="s">
+        <v>343</v>
+      </c>
+      <c r="G98" t="s">
+        <v>283</v>
+      </c>
+      <c r="H98" t="s">
+        <v>344</v>
+      </c>
+      <c r="I98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>345</v>
+      </c>
+      <c r="B99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C99" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
+        <v>91</v>
+      </c>
+      <c r="G99" t="s">
+        <v>273</v>
+      </c>
+      <c r="H99" t="s">
+        <v>346</v>
+      </c>
+      <c r="I99" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>347</v>
+      </c>
+      <c r="B100" t="s">
+        <v>151</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" t="s">
+        <v>86</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>348</v>
+      </c>
+      <c r="G100" t="s">
+        <v>349</v>
+      </c>
+      <c r="H100" t="s">
+        <v>350</v>
+      </c>
+      <c r="I100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" t="s">
+        <v>155</v>
+      </c>
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" t="s">
+        <v>348</v>
+      </c>
+      <c r="G101" t="s">
+        <v>71</v>
+      </c>
+      <c r="H101" t="s">
+        <v>352</v>
+      </c>
+      <c r="I101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>353</v>
+      </c>
+      <c r="B102" t="s">
+        <v>64</v>
+      </c>
+      <c r="C102" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
+        <v>35</v>
+      </c>
+      <c r="G102" t="s">
+        <v>252</v>
+      </c>
+      <c r="H102" t="s">
+        <v>354</v>
+      </c>
+      <c r="I102" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>355</v>
+      </c>
+      <c r="B103" t="s">
+        <v>356</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" t="s">
+        <v>152</v>
+      </c>
+      <c r="G103" t="s">
+        <v>161</v>
+      </c>
+      <c r="H103" t="s">
+        <v>357</v>
+      </c>
+      <c r="I103" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
